--- a/output/result/voting/qwen3-32b-core-All-Avg64ofB128-AllAblation-base.xlsx
+++ b/output/result/voting/qwen3-32b-core-All-Avg64ofB128-AllAblation-base.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,16 +467,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6395833333333333</v>
+        <v>0.6322916666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7203282828282829</v>
+        <v>0.7192234848484849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8828125</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7692708333333333</v>
+        <v>0.7723958333333333</v>
       </c>
       <c r="F2" t="n">
         <v>0.9333333333333333</v>
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6484375</v>
+        <v>0.6416666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7241950757575758</v>
+        <v>0.7230902777777778</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8864583333333333</v>
+        <v>0.8901041666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7921875</v>
+        <v>0.790625</v>
       </c>
       <c r="F3" t="n">
         <v>0.9333333333333333</v>
@@ -511,16 +511,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6385416666666667</v>
+        <v>0.6322916666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7200915404040404</v>
+        <v>0.7186710858585859</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8828125</v>
+        <v>0.8838541666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7697916666666667</v>
+        <v>0.7734375</v>
       </c>
       <c r="F4" t="n">
         <v>0.9333333333333333</v>
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6479166666666667</v>
+        <v>0.64375</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7229324494949495</v>
+        <v>0.7196969696969697</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8869791666666667</v>
+        <v>0.8911458333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7911458333333333</v>
+        <v>0.7869791666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9328125</v>
+        <v>0.9322916666666666</v>
       </c>
     </row>
     <row r="6">
@@ -555,16 +555,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.65</v>
+        <v>0.6453125</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7250631313131313</v>
+        <v>0.7234059343434344</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8854166666666666</v>
+        <v>0.8911458333333333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7895833333333333</v>
+        <v>0.7880208333333333</v>
       </c>
       <c r="F6" t="n">
         <v>0.9333333333333333</v>
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6447916666666667</v>
+        <v>0.6375</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7275094696969697</v>
+        <v>0.7250631313131313</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8911458333333333</v>
+        <v>0.8895833333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7875</v>
+        <v>0.7854166666666667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9322916666666666</v>
+        <v>0.93125</v>
       </c>
     </row>
     <row r="8">
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6494791666666667</v>
+        <v>0.6421875</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7233270202020202</v>
+        <v>0.719854797979798</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8869791666666667</v>
+        <v>0.8895833333333333</v>
       </c>
       <c r="E8" t="n">
-        <v>0.790625</v>
+        <v>0.7869791666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9328125</v>
+        <v>0.9322916666666666</v>
       </c>
     </row>
     <row r="9">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6442708333333333</v>
+        <v>0.6359375</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7274305555555556</v>
+        <v>0.7250631313131313</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8901041666666667</v>
+        <v>0.8911458333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7869791666666667</v>
+        <v>0.7854166666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9322916666666666</v>
+        <v>0.9286458333333333</v>
       </c>
     </row>
     <row r="10">
@@ -643,16 +643,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6223958333333334</v>
+        <v>0.6208333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7054924242424242</v>
+        <v>0.7043876262626263</v>
       </c>
       <c r="D10" t="n">
-        <v>0.86875</v>
+        <v>0.8755208333333333</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7708333333333334</v>
+        <v>0.7713541666666667</v>
       </c>
       <c r="F10" t="n">
         <v>0.9333333333333333</v>
@@ -665,85 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6265625</v>
+        <v>0.621875</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7034406565656566</v>
+        <v>0.7004419191919192</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8932291666666666</v>
+        <v>0.8994791666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8041666666666667</v>
+        <v>0.80625</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9317708333333333</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.6208333333333333</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.7029671717171717</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8645833333333334</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.7697916666666667</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BoN</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.5947916666666667</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.7200126262626263</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.8729166666666667</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.7401041666666667</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.8708333333333333</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MoB-Adaptive</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.6572916666666667</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.7208017676767676</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.884375</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.78125</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.9265625</v>
+        <v>0.9296875</v>
       </c>
     </row>
   </sheetData>
